--- a/data/analysis_pixtral_12b_panns/multimodal_event_eval_pixtral_12b_panns_w5_0s_h2_5s.xlsx
+++ b/data/analysis_pixtral_12b_panns/multimodal_event_eval_pixtral_12b_panns_w5_0s_h2_5s.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="52">
   <si>
     <t>event</t>
   </si>
@@ -143,6 +143,9 @@
   </si>
   <si>
     <t>sound: skidding(0-120), visual: enter_or_exit_vehicle(144-144), visual: enter_or_exit_vehicle(240-240), visual: running(24-240), visual: suspicious_near_vehicle(120-240), visual: suspicious_near_vehicle(96-96), visual: suspicious_near_vehicle(120-120), visual: vehicle_collision(72-240), visual: vehicle_collision(72-72), visual: vehicle_collision(96-216)</t>
+  </si>
+  <si>
+    <t>visual: enter_or_exit_vehicle(144-144), visual: enter_or_exit_vehicle(240-240), visual: running(24-240), visual: suspicious_near_vehicle(120-240), visual: suspicious_near_vehicle(96-96), visual: suspicious_near_vehicle(120-120), visual: vehicle_collision(72-240), visual: vehicle_collision(72-72), visual: vehicle_collision(96-216)</t>
   </si>
   <si>
     <t>sound: horn(0-120), sound: gunshot_or_explosion(60-180), sound: engine(120-240), visual: enter_or_exit_vehicle(120-216), visual: enter_or_exit_vehicle(144-144), visual: enter_or_exit_vehicle(120-216), visual: suspicious_near_vehicle(168-240), visual: suspicious_near_vehicle(144-144), visual: suspicious_near_vehicle(168-240), visual: vehicle_collision(120-240), visual: vehicle_collision(192-240)</t>
@@ -666,22 +669,22 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>0.8</v>
+        <v>0.714</v>
       </c>
       <c r="C5">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>5</v>
@@ -956,7 +959,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -991,54 +994,71 @@
       </c>
       <c r="E2" t="s">
         <v>32</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>17</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
         <v>17</v>
       </c>
       <c r="B3" t="s">
@@ -1051,7 +1071,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1089,13 +1109,13 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>34</v>
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1139,7 +1159,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1183,7 +1203,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1200,7 +1220,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1244,7 +1264,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1332,7 +1352,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1376,7 +1396,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1420,7 +1440,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1464,7 +1484,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1508,7 +1528,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1552,7 +1572,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1569,7 +1589,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1613,7 +1633,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1657,7 +1677,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1701,7 +1721,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1745,7 +1765,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1833,7 +1853,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1877,7 +1897,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
